--- a/12525035.xlsx
+++ b/12525035.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\~\daily-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDA193E-9CAF-4E28-984E-F0093EB260CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB3DC1F-E4B1-4FE3-AB4F-CB5CCA5B75B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t xml:space="preserve"> khjhjhbjh</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> xco</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1100,9 @@
         <v>54</v>
       </c>
       <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
+      <c r="F10" s="14" t="s">
+        <v>56</v>
+      </c>
       <c r="G10" s="14"/>
       <c r="H10" s="14"/>
       <c r="I10" s="15" t="str">
